--- a/profiling/tools/scenario_callback30/scenarios.xlsx
+++ b/profiling/tools/scenario_callback30/scenarios.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -518,7 +518,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>상위N_최소: 상위 N 안에 대상이 최소 K개 (값 'N:K') · 상위N_최대: 상위 N 안에 대상이 최대 K개 · 조회수순: 30개가 조회수 내림차순 · 모드간_동일: 두 모드의 30개가 같음 · 순위_앞섬: 전체 순위에서 대상A 최고 순위가 대상B 보다 앞('A&gt;B')</t>
+          <t>상위N_최소 · 상위N_최대: 상위 N 안에 대상이 최소/최대 K개(값 'N:K') · 조회수순 · 모드간_동일 · 순위_앞섬('A&gt;B', 전체 점수 순위) · 이름_최소: 상위 N 상품명에 정규식(대상)이 맞는 상품 K개 이상 · 종수_최소: 상위 N 의 소분류 K종 이상 · 태그_포함 / 태그_제외: 추출된 선호 태그 중 정규식(대상)에 맞는 것이 있음 / 없음 · 태그_없음: 선호 태그 0개</t>
         </is>
       </c>
     </row>
@@ -591,6 +591,18 @@
       <c r="B12" s="3" t="inlineStr">
         <is>
           <t>임베딩 비교 실험(tools/embed_compare)의 입력 — 4축(IP·브랜드·카테고리·특징) 양의 태그. '추출 모델' 열로 태그 세트를 구분한다: claude-opus-5-5 = 대화 중 Claude 가 수작업으로 적음(고정 프롬프트 없음) · gemma4:12b · qwen3.5:9b 등 = tools/embed_compare/extract_tags.py 가 로컬 Ollama 로 같은 프롬프트로 추출(다시 돌리면 그 모델 행만 바뀜). 실행: run --tagger &lt;모델&gt;. 1~3점·비선호는 태그로 쓰지 않고 편향·감점으로. 태그가 없으면 조회수 순위로 대체. 30개 콜백 검증(run.py)은 이 시트를 읽지 않는다</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>기대 — 조건 · 등급 · 성격</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>조건: '태그=끔'(추출기 꺼짐) · '태그=켬'(TAGGER=ollama 등) · 비면 언제나. ';' 로 여럿(고르기=d · 모델=gemma 처럼). 등급: 필수(실패하면 하네스 실패) · 관찰(보고만 — 모델 · 프롬프트 품질 비교용). 성격: 계약 · 별점 · 회귀 · 태그품질 · 취향 · 섞임. 취향 · 섞임 문턱은 10-12 gemma4:12b 실측에 여유를 둔 값(10-12 작성)</t>
         </is>
       </c>
     </row>
@@ -4758,754 +4770,2035 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:I46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="9" customWidth="1" min="5" max="5"/>
-    <col width="50" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="46" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="7" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>번호</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>모드</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>검사</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="4" t="inlineStr">
         <is>
           <t>대상</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="4" t="inlineStr">
         <is>
           <t>값</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="4" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>조건</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>등급</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>성격</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>U01</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>상위N_최대</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>대분류:4</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>30:0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>비선호 식품 제외</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>필수</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>계약</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>U05</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
         <is>
           <t>both</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>상위N_최대</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>대분류:6</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>30:0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>디지털·가전 — 제외 또는 D 하드 제외</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>필수</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>계약</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>U08</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>상위N_최대</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>대분류:1,2,3,4,5</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>30:0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>다섯 대분류 제외</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>필수</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>계약</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>U08</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>penalty</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>모드간_동일</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>비선호 아닌 상품이 충분 — 두 모드 30개가 같음</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>필수</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>계약</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>U09</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>상위N_최대</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>대분류:1</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>30:0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>뷰티 비선호 — 향수 5점이어도 30개에 없음(D 하드 제외)</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>필수</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>계약</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>U09</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>penalty</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>순위_앞섬</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>소분류:13&gt;소분류:11</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>전체 점수 순위에서 향수(편향 가산)가 스킨케어보다 앞</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>필수</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>계약</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>U10</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>상위N_최대</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>대분류:8</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>30:0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>ID가 틀려도 이름으로 유아·키즈 제외</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>필수</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>계약</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>U06</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>penalty</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>모드간_동일</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>비선호가 없으면 두 모드 같음</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>필수</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>계약</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>U01</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>상위N_최대</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>소분류:22</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>30:0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2점 케이크는 30개 밖</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>필수</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>별점</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>U02</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>상위N_최대</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>소분류:19</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>30:0</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2점 신발은 30개 밖</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>필수</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>별점</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>U07</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>상위N_최대</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>소분류:19</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>30:0</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>1점 신발</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>필수</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>별점</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>U07</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>상위N_최대</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>소분류:17</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>30:0</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2점 의류</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>필수</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>별점</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>U07</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>상위N_최대</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>소분류:29</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>30:0</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>1점 과일·견과</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>필수</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>별점</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>U07</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>상위N_최대</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>소분류:28</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>30:0</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2점 건강식품</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>필수</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>별점</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>U01</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
         <is>
           <t>상위N_최소</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>소분류:13</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>10:1</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>5점 향수가 상위 10 안에</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>5점 향수가 상위 10 안</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>태그=끔</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>필수</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>회귀</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>U02</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>상위N_최소</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>소분류:44</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>10:1</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>5점 영상·음향</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>태그=끔</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>필수</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>회귀</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>U02</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>상위N_최소</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>소분류:43</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>10:1</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>5점 모바일·PC</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>태그=끔</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>필수</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>회귀</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>U03</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>상위N_최소</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>소분류:58</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>10:5</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>편향 +1.0 — 상위 10 중 절반 이상 출산·육아</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>태그=끔</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>필수</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>회귀</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>U04</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>상위N_최소</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>소분류:35</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>10:1</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>5점 인테리어</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>태그=끔</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>필수</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>회귀</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>U04</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>상위N_최소</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>소분류:54</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>10:1</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>5점 스포츠·레저</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>태그=끔</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>필수</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>회귀</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>U05</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>상위N_최소</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>소분류:24</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>10:1</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>커피·차</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>태그=끔</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>필수</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>회귀</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>U05</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>상위N_최소</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>소분류:22</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>10:1</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>케이크</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>태그=끔</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>필수</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>회귀</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>U06</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>조회수순</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>리뷰 · 태그 없음 → 조회수 내림차순</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>태그=끔</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>필수</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>회귀</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>U01</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>both</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>상위N_최대</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>소분류:22</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>30:0</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>2점 케이크는 30개 밖</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>태그_포함</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>향수</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>5점 향수 리뷰 + 취향 문장</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>태그=켬</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>관찰</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>태그품질</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
         <is>
           <t>U01</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>exclude</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>상위N_최대</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>대분류:4</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>30:0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>비선호 식품 제외</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>태그_제외</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>케이크</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2점 케이크로 선호 태그를 만들지 않음</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>태그=켬</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>관찰</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>태그품질</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
         <is>
           <t>U02</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>both</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>태그_포함</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>헤드폰|노이즈</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>5점 헤드폰 리뷰</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>태그=켬</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>관찰</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>태그품질</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>U02</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>태그_포함</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>노트북|거치대</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>5점 노트북 거치대 리뷰</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>태그=켬</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>관찰</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>태그품질</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>U02</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>태그_제외</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>신발|운동화|스니커즈</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2점 신발로 선호 태그를 만들지 않음</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>태그=켬</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>관찰</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>태그품질</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>U03</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>태그_포함</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>출산|아기|신생아|유아</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>육아 리뷰 3건 + 취향 문장 — 품목 태그</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>태그=켬</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>관찰</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>태그품질</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>U04</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>태그_포함</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>춘식</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>취향 문장 + 춘식이 보냉백 5점</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>태그=켬</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>관찰</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>태그품질</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>U04</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>태그_포함</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>산리오|한교동</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>취향 문장 + 한교동 테이블 5점</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>태그=켬</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>관찰</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>태그품질</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>U05</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>태그_포함</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>커피</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>취향 문장 + 커피 4점</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>태그=켬</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>관찰</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>태그품질</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>U05</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>태그_포함</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>케이크|디저트</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>취향 문장 + 케이크 5점</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>태그=켬</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>관찰</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>태그품질</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>U07</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>태그_없음</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>1~2점 리뷰뿐 → 선호 태그 없음</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>태그=켬</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>관찰</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>태그품질</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>U09</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>태그_포함</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>향수|조말론</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>향수 5점 2건(뷰티는 비선호여도 태그는 남김)</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>태그=켬</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>관찰</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>태그품질</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>U10</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>태그_포함</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>헤드폰|소니</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>5점 헤드폰(1점 중복 리뷰는 버려짐)</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>태그=켬</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>관찰</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>태그품질</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>U01</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
         <is>
           <t>상위N_최소</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>소분류:13</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>30:5</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>향수 계열이 30개에 5개 이상</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>태그=켬</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>관찰</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>취향</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>U02</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>상위N_최소</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
         <is>
           <t>소분류:44</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>10:1</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>5점 영상·음향</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>30:5</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>영상·음향 5개 이상</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>태그=켬</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>관찰</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>취향</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
         <is>
           <t>U02</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>both</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>상위N_최소</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D40" t="inlineStr">
         <is>
           <t>소분류:43</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>10:1</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>5점 모바일·PC</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>U02</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>30:3</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>모바일·PC 3개 이상</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>태그=켬</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>관찰</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>취향</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>U03</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
         <is>
           <t>both</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>상위N_최대</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>소분류:19</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>30:0</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>2점 신발은 30개 밖</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>상위N_최소</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>소분류:58</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>30:8</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>출산·육아 30개 중 8개 이상</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>태그=켬</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>관찰</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>취향</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
         <is>
           <t>U03</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>both</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t>상위N_최소</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>소분류:58</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>10:5</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>편향 +1.0 — 상위 10 중 절반 이상 출산·육아</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>10:3</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>상위 10 중 출산·육아 3개 이상</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>태그=켬</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>관찰</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>취향</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
         <is>
           <t>U04</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>both</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>이름_최소</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>춘식|산리오|카카오프렌즈|헬로키티|쿠로미|시나모롤|한교동|라이언</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>30:15</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>좋아한 캐릭터 상품 30개 중 15개 이상</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>태그=켬</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>관찰</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>취향</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>U05</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
         <is>
           <t>상위N_최소</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>소분류:35</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>10:1</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>5점 인테리어</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>U04</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>소분류:24</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>30:5</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>커피·차 5개 이상</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>태그=켬</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>관찰</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>취향</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>U06</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
         <is>
           <t>both</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>종수_최소</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>30:12</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>모호한 태그 하나로 몰리지 않음 — 소분류 12종 이상</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>태그=켬</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>관찰</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>섞임</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>U09</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
         <is>
           <t>상위N_최소</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>소분류:54</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>10:1</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>5점 스포츠·레저</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>U05</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>both</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>상위N_최소</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>소분류:24</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>10:1</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>커피·차</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>U05</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>both</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>상위N_최소</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>소분류:22</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>10:1</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>케이크</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>U05</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>both</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>상위N_최대</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>대분류:6</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>30:0</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>디지털·가전 — 제외 또는 −2.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>U06</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>both</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>조회수순</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr"/>
-      <c r="E14" s="2" t="inlineStr"/>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>리뷰 없음 → 조회수 내림차순</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>U06</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>penalty</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>모드간_동일</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr"/>
-      <c r="E15" s="2" t="inlineStr"/>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>비선호가 없으면 두 모드 같음</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>U07</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>both</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>상위N_최대</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>소분류:19</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>30:0</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>1점 신발</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>U07</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>both</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>상위N_최대</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>소분류:17</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>30:0</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>2점 의류</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>U07</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>both</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>상위N_최대</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>소분류:29</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>30:0</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>1점 과일·견과</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>U07</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>both</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>상위N_최대</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>소분류:28</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>30:0</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>2점 건강식품</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>U08</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>exclude</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>상위N_최대</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>대분류:1,2,3,4,5</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>30:0</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>다섯 대분류 제외</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>U08</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>penalty</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>모드간_동일</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr"/>
-      <c r="E21" s="2" t="inlineStr"/>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>비선호 아닌 상품이 충분 — 30개가 제외 모드와 같음</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>U09</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>both</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>상위N_최대</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>대분류:1</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>30:0</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>뷰티는 30개에 없음(제외 또는 −2.0 + 1.0)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>U09</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>penalty</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>순위_앞섬</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>소분류:13&gt;소분류:11</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr"/>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>편향이 가산돼 향수가 스킨케어보다 앞(전체 순위)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>U10</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>exclude</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>상위N_최대</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>대분류:8</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>30:0</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>ID가 틀려도 이름으로 유아·키즈 제외</t>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>소분류:36</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>30:5</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>뷰티 대신 생활 향 제품(홈프래그런스) 5개 이상</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>태그=켬</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>관찰</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>취향</t>
         </is>
       </c>
     </row>
